--- a/artfynd/A 7961-2022 artfynd.xlsx
+++ b/artfynd/A 7961-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7961-2022 artfynd.xlsx
+++ b/artfynd/A 7961-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,6 +1369,934 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118977570</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hukkajärvi (Hukkajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>816949</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7525241</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118975272</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79109</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>817155</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7525198</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118974270</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79476</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>817271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7525363</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118977406</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>817062</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7525164</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118977467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91786</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>817015</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7525192</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118974164</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78491</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>817287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7525388</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118973848</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90529</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hukkajärvi (Hukkajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>817194</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7525500</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118974019</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74603</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>817274</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7525441</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118974143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>817287</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7525388</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på en asp.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7961-2022 artfynd.xlsx
+++ b/artfynd/A 7961-2022 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118975272</v>
+        <v>118973848</v>
       </c>
       <c r="B9" t="n">
-        <v>79109</v>
+        <v>90529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Hukkajärvi (Hukkajärvi), Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817155</v>
+        <v>817194</v>
       </c>
       <c r="R9" t="n">
-        <v>7525198</v>
+        <v>7525500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118974270</v>
+        <v>118977406</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>91798</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817271</v>
+        <v>817062</v>
       </c>
       <c r="R10" t="n">
-        <v>7525363</v>
+        <v>7525164</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118977406</v>
+        <v>118974143</v>
       </c>
       <c r="B11" t="n">
-        <v>91798</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,38 +1689,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Laihajärvi (Laihajärvi), Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>817062</v>
+        <v>817287</v>
       </c>
       <c r="R11" t="n">
-        <v>7525164</v>
+        <v>7525388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,6 +1758,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på en asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118977467</v>
+        <v>118975272</v>
       </c>
       <c r="B12" t="n">
-        <v>91786</v>
+        <v>79109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,25 +1801,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1819,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>817015</v>
+        <v>817155</v>
       </c>
       <c r="R12" t="n">
-        <v>7525192</v>
+        <v>7525198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118974164</v>
+        <v>118974019</v>
       </c>
       <c r="B13" t="n">
-        <v>78491</v>
+        <v>74603</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1897,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1921,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>817287</v>
+        <v>817274</v>
       </c>
       <c r="R13" t="n">
-        <v>7525388</v>
+        <v>7525441</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118973848</v>
+        <v>118974164</v>
       </c>
       <c r="B14" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,34 +2009,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hukkajärvi (Hukkajärvi), Nb</t>
+          <t>Laihajärvi (Laihajärvi), Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817194</v>
+        <v>817287</v>
       </c>
       <c r="R14" t="n">
-        <v>7525500</v>
+        <v>7525388</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118974019</v>
+        <v>118977467</v>
       </c>
       <c r="B15" t="n">
-        <v>74603</v>
+        <v>91786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2125,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817274</v>
+        <v>817015</v>
       </c>
       <c r="R15" t="n">
-        <v>7525441</v>
+        <v>7525192</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118974143</v>
+        <v>118974270</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>79476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,43 +2209,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Laihajärvi (Laihajärvi), Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817287</v>
+        <v>817271</v>
       </c>
       <c r="R16" t="n">
-        <v>7525388</v>
+        <v>7525363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,11 +2273,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på en asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 7961-2022 artfynd.xlsx
+++ b/artfynd/A 7961-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111297994</v>
+        <v>111298099</v>
       </c>
       <c r="B2" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817065.8281341128</v>
+        <v>817222</v>
       </c>
       <c r="R2" t="n">
-        <v>7525163.567819493</v>
+        <v>7525324</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,19 +746,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111298135</v>
+        <v>111298160</v>
       </c>
       <c r="B3" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817222.6979034413</v>
+        <v>817222</v>
       </c>
       <c r="R3" t="n">
-        <v>7525323.512308424</v>
+        <v>7525324</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,19 +847,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,16 +880,11 @@
         <v>111297953</v>
       </c>
       <c r="B4" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817013.4098527509</v>
+        <v>817013</v>
       </c>
       <c r="R4" t="n">
-        <v>7525202.863409569</v>
+        <v>7525203</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -983,19 +948,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111298009</v>
+        <v>111297994</v>
       </c>
       <c r="B5" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817091.6737603555</v>
+        <v>817066</v>
       </c>
       <c r="R5" t="n">
-        <v>7525169.015249422</v>
+        <v>7525164</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,19 +1049,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111298160</v>
+        <v>111298009</v>
       </c>
       <c r="B6" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817222.6979034413</v>
+        <v>817092</v>
       </c>
       <c r="R6" t="n">
-        <v>7525323.512308424</v>
+        <v>7525169</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1215,19 +1150,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111298099</v>
+        <v>118977467</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,40 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nälkejärvi, Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>817222.6979034413</v>
+        <v>817015</v>
       </c>
       <c r="R7" t="n">
-        <v>7525323.512308424</v>
+        <v>7525192</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,34 +1259,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka, Robert Flygare</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118973848</v>
+        <v>118977406</v>
       </c>
       <c r="B8" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,34 +1288,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hukkajärvi (Hukkajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>817194</v>
+        <v>817062</v>
       </c>
       <c r="R8" t="n">
-        <v>7525500</v>
+        <v>7525164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,50 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118974270</v>
+        <v>118977570</v>
       </c>
       <c r="B9" t="n">
-        <v>79496</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Hukkajärvi, Hukkajärvi, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817271</v>
+        <v>816949</v>
       </c>
       <c r="R9" t="n">
-        <v>7525363</v>
+        <v>7525241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,50 +1471,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118977406</v>
+        <v>118974164</v>
       </c>
       <c r="B10" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817062</v>
+        <v>817287</v>
       </c>
       <c r="R10" t="n">
-        <v>7525164</v>
+        <v>7525388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,12 +1571,7 @@
         <v>118974019</v>
       </c>
       <c r="B11" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1599,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1782,12 +1668,7 @@
         <v>118975272</v>
       </c>
       <c r="B12" t="n">
-        <v>79129</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1696,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1881,55 +1762,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118974143</v>
+        <v>118974270</v>
       </c>
       <c r="B13" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>817287</v>
+        <v>817271</v>
       </c>
       <c r="R13" t="n">
-        <v>7525388</v>
+        <v>7525363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,16 +1835,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på en asp.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -1993,15 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118974164</v>
+        <v>118974077</v>
       </c>
       <c r="B14" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,34 +1870,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817287</v>
+        <v>817294</v>
       </c>
       <c r="R14" t="n">
-        <v>7525388</v>
+        <v>7525413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,11 +1937,16 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack i en asp.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2095,50 +1966,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118977467</v>
+        <v>118974143</v>
       </c>
       <c r="B15" t="n">
-        <v>91809</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Laihajärvi (Laihajärvi), Nb</t>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817015</v>
+        <v>817287</v>
       </c>
       <c r="R15" t="n">
-        <v>7525192</v>
+        <v>7525388</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,11 +2044,16 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på en asp.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2194,108 +2070,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>118977570</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4366</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Hukkajärvi (Hukkajärvi), Nb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>816949</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7525241</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Junosuando</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7961-2022 artfynd.xlsx
+++ b/artfynd/A 7961-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111297953</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111297994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298009</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118977467</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118977406</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118977570</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974164</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974019</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118975272</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974077</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,8 +2140,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974143</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>